--- a/public/assets/templates/statistics/统计汇总-区内明细.xlsx
+++ b/public/assets/templates/statistics/统计汇总-区内明细.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="15300"/>
+    <workbookView windowHeight="15300"/>
   </bookViews>
   <sheets>
     <sheet name="区内明细" sheetId="1" r:id="rId1"/>
@@ -1346,27 +1346,37 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AF2"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1"/>
+  <sheetFormatPr defaultColWidth="8.88461538461539" defaultRowHeight="16.8" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="10.2222222222222" customWidth="1"/>
-    <col min="3" max="3" width="12.7685185185185" customWidth="1"/>
-    <col min="4" max="4" width="16.6666666666667" customWidth="1"/>
-    <col min="8" max="8" width="24.8425925925926" customWidth="1"/>
-    <col min="9" max="9" width="20.8425925925926" customWidth="1"/>
-    <col min="10" max="10" width="8.15740740740741" customWidth="1"/>
-    <col min="11" max="11" width="16.4444444444444" customWidth="1"/>
-    <col min="13" max="13" width="23.3333333333333" customWidth="1"/>
-    <col min="14" max="14" width="13.4444444444444" customWidth="1"/>
-    <col min="16" max="16" width="21.8425925925926" customWidth="1"/>
-    <col min="17" max="17" width="25.4444444444444" customWidth="1"/>
-    <col min="21" max="21" width="12.7685185185185" customWidth="1"/>
+    <col min="1" max="1" width="10.2211538461538" customWidth="1"/>
+    <col min="3" max="3" width="12.7692307692308" customWidth="1"/>
+    <col min="4" max="4" width="16.6634615384615" customWidth="1"/>
+    <col min="6" max="6" width="18.2596153846154" customWidth="1"/>
+    <col min="7" max="7" width="11.6923076923077" customWidth="1"/>
+    <col min="8" max="8" width="24.8461538461538" customWidth="1"/>
+    <col min="9" max="9" width="20.8461538461538" customWidth="1"/>
+    <col min="10" max="10" width="8.15384615384615" customWidth="1"/>
+    <col min="11" max="11" width="16.4423076923077" customWidth="1"/>
+    <col min="13" max="13" width="23.3365384615385" customWidth="1"/>
+    <col min="14" max="14" width="15.2211538461538" customWidth="1"/>
+    <col min="15" max="15" width="15.0576923076923" customWidth="1"/>
+    <col min="16" max="16" width="21.8461538461538" customWidth="1"/>
+    <col min="17" max="17" width="25.4423076923077" customWidth="1"/>
+    <col min="18" max="18" width="13.2980769230769" customWidth="1"/>
+    <col min="19" max="20" width="12.6538461538462" customWidth="1"/>
+    <col min="21" max="21" width="12.7692307692308" customWidth="1"/>
     <col min="22" max="22" width="20" customWidth="1"/>
-    <col min="23" max="25" width="24.8425925925926" customWidth="1"/>
+    <col min="23" max="25" width="24.8461538461538" customWidth="1"/>
     <col min="26" max="26" width="20" customWidth="1"/>
-    <col min="27" max="28" width="15.1574074074074" customWidth="1"/>
+    <col min="27" max="28" width="15.1538461538462" customWidth="1"/>
+    <col min="29" max="29" width="20.0288461538462" customWidth="1"/>
+    <col min="30" max="30" width="21.625" customWidth="1"/>
+    <col min="31" max="31" width="23.0673076923077" customWidth="1"/>
+    <col min="32" max="32" width="25.3173076923077" customWidth="1"/>
+    <col min="33" max="33" width="15.2115384615385" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.8" spans="1:32">
+    <row r="1" ht="17" spans="1:32">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
